--- a/DigitalWars.Server/Initializers/DigitalWars_UserInitialization.xlsx
+++ b/DigitalWars.Server/Initializers/DigitalWars_UserInitialization.xlsx
@@ -604,7 +604,7 @@
     <t>Próbujesz udoskonalać proces jednak bariery wewnętrzne skutecznie to blokują. Pomyśl nad analizą danych czy zwiększeniem świadomości zespołu.</t>
   </si>
   <si>
-    <t>Cards_Weights_Id</t>
+    <t>CardsWeights_Id</t>
   </si>
   <si>
     <t>Weights_X</t>
@@ -12942,7 +12942,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>190</v>
       </c>
       <c r="B1" s="10" t="s">

--- a/DigitalWars.Server/Initializers/DigitalWars_UserInitialization.xlsx
+++ b/DigitalWars.Server/Initializers/DigitalWars_UserInitialization.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="194">
   <si>
     <t>Name</t>
   </si>
@@ -234,7 +234,7 @@
     <t>Zespół spędza więcej czasu na naprawianiu starych błędów, niż na wdrażaniu nowych rozwiązań, co spowalnia tempo całej transformacji. Dwa następne poruszenia na planszy będą o 50% krótsze.</t>
   </si>
   <si>
-    <t>Card_Id</t>
+    <t>Cards_Id</t>
   </si>
   <si>
     <t>Decisions_Id</t>
@@ -613,12 +613,6 @@
     <t>Weights_Y</t>
   </si>
   <si>
-    <t>Booster_X</t>
-  </si>
-  <si>
-    <t>Booster_Y</t>
-  </si>
-  <si>
     <t>Enablers_Id</t>
   </si>
 </sst>
@@ -626,7 +620,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -635,6 +629,10 @@
     </font>
     <font>
       <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
@@ -659,6 +657,10 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -675,7 +677,7 @@
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -686,6 +688,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF9900"/>
         <bgColor rgb="FFFF9900"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -706,51 +714,81 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="30">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2163,663 +2201,663 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>195</v>
+      <c r="B1" s="17" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="9">
+      <c r="A2" s="12">
         <v>17.0</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="9">
+      <c r="A3" s="12">
         <v>21.0</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="9">
+      <c r="A4" s="12">
         <v>21.0</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="11">
         <v>6.0</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="9">
+      <c r="A5" s="12">
         <v>8.0</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="11">
         <v>21.0</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="9">
+      <c r="A6" s="12">
         <v>8.0</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="11">
         <v>17.0</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="9">
+      <c r="A7" s="12">
         <v>30.0</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="11">
         <v>8.0</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="9">
+      <c r="A8" s="12">
         <v>7.0</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="11">
         <v>30.0</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="9">
+      <c r="A9" s="12">
         <v>13.0</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="11">
         <v>7.0</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="9">
+      <c r="A10" s="12">
         <v>13.0</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="11">
         <v>8.0</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="9">
+      <c r="A11" s="12">
         <v>13.0</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="11">
         <v>21.0</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="9">
+      <c r="A12" s="12">
         <v>25.0</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="9">
+      <c r="A13" s="12">
         <v>25.0</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="11">
         <v>8.0</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="9">
+      <c r="A14" s="12">
         <v>27.0</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="11">
         <v>25.0</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="9">
+      <c r="A15" s="12">
         <v>101.0</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="9">
+      <c r="A16" s="12">
         <v>102.0</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="9">
+      <c r="A17" s="12">
         <v>103.0</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="9">
+      <c r="A18" s="12">
         <v>104.0</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
-      <c r="A19" s="9">
+      <c r="A19" s="12">
         <v>105.0</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="A20" s="9">
+      <c r="A20" s="12">
         <v>106.0</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="21" ht="12.75" customHeight="1">
-      <c r="A21" s="9">
+      <c r="A21" s="12">
         <v>107.0</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
-      <c r="A22" s="9">
+      <c r="A22" s="12">
         <v>108.0</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="9">
+      <c r="A23" s="12">
         <v>109.0</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
-      <c r="A24" s="9">
+      <c r="A24" s="12">
         <v>110.0</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
-      <c r="A25" s="9">
+      <c r="A25" s="12">
         <v>111.0</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
-      <c r="A26" s="9">
+      <c r="A26" s="12">
         <v>112.0</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
-      <c r="A27" s="9">
+      <c r="A27" s="12">
         <v>201.0</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="9">
+      <c r="A28" s="12">
         <v>202.0</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="29" ht="12.75" customHeight="1">
-      <c r="A29" s="9">
+      <c r="A29" s="12">
         <v>203.0</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="A30" s="9">
+      <c r="A30" s="12">
         <v>204.0</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="31" ht="12.75" customHeight="1">
-      <c r="A31" s="9">
+      <c r="A31" s="12">
         <v>205.0</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="9">
+      <c r="A32" s="12">
         <v>206.0</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="9">
+      <c r="A33" s="12">
         <v>207.0</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="9">
+      <c r="A34" s="12">
         <v>208.0</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="9">
+      <c r="A35" s="12">
         <v>209.0</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="9">
+      <c r="A36" s="12">
         <v>210.0</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="9">
+      <c r="A37" s="12">
         <v>211.0</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="9">
+      <c r="A38" s="12">
         <v>212.0</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="9">
+      <c r="A39" s="12">
         <v>213.0</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="9">
+      <c r="A40" s="12">
         <v>214.0</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="9">
+      <c r="A41" s="12">
         <v>215.0</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="9">
+      <c r="A42" s="12">
         <v>216.0</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="9">
+      <c r="A43" s="12">
         <v>217.0</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="9">
+      <c r="A44" s="12">
         <v>218.0</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="9">
+      <c r="A45" s="12">
         <v>219.0</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="9">
+      <c r="A46" s="12">
         <v>220.0</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="9">
+      <c r="A47" s="12">
         <v>221.0</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="9">
+      <c r="A48" s="12">
         <v>222.0</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="11">
         <v>23.0</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="9">
+      <c r="A49" s="12">
         <v>101.0</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="A50" s="9">
+      <c r="A50" s="12">
         <v>102.0</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="A51" s="9">
+      <c r="A51" s="12">
         <v>103.0</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="A52" s="9">
+      <c r="A52" s="12">
         <v>104.0</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="A53" s="9">
+      <c r="A53" s="12">
         <v>105.0</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="A54" s="9">
+      <c r="A54" s="12">
         <v>106.0</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="A55" s="9">
+      <c r="A55" s="12">
         <v>107.0</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="A56" s="9">
+      <c r="A56" s="12">
         <v>108.0</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="A57" s="9">
+      <c r="A57" s="12">
         <v>109.0</v>
       </c>
-      <c r="B57" s="8">
+      <c r="B57" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="A58" s="9">
+      <c r="A58" s="12">
         <v>110.0</v>
       </c>
-      <c r="B58" s="8">
+      <c r="B58" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="A59" s="9">
+      <c r="A59" s="12">
         <v>111.0</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="A60" s="9">
+      <c r="A60" s="12">
         <v>112.0</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B60" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="9">
+      <c r="A61" s="12">
         <v>201.0</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="A62" s="9">
+      <c r="A62" s="12">
         <v>202.0</v>
       </c>
-      <c r="B62" s="8">
+      <c r="B62" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="63" ht="12.75" customHeight="1">
-      <c r="A63" s="9">
+      <c r="A63" s="12">
         <v>203.0</v>
       </c>
-      <c r="B63" s="8">
+      <c r="B63" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="A64" s="9">
+      <c r="A64" s="12">
         <v>204.0</v>
       </c>
-      <c r="B64" s="8">
+      <c r="B64" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="65" ht="12.75" customHeight="1">
-      <c r="A65" s="9">
+      <c r="A65" s="12">
         <v>205.0</v>
       </c>
-      <c r="B65" s="8">
+      <c r="B65" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="66" ht="12.75" customHeight="1">
-      <c r="A66" s="9">
+      <c r="A66" s="12">
         <v>206.0</v>
       </c>
-      <c r="B66" s="8">
+      <c r="B66" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="67" ht="12.75" customHeight="1">
-      <c r="A67" s="9">
+      <c r="A67" s="12">
         <v>207.0</v>
       </c>
-      <c r="B67" s="8">
+      <c r="B67" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="A68" s="9">
+      <c r="A68" s="12">
         <v>208.0</v>
       </c>
-      <c r="B68" s="8">
+      <c r="B68" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="A69" s="9">
+      <c r="A69" s="12">
         <v>209.0</v>
       </c>
-      <c r="B69" s="8">
+      <c r="B69" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="A70" s="9">
+      <c r="A70" s="12">
         <v>210.0</v>
       </c>
-      <c r="B70" s="8">
+      <c r="B70" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="71" ht="12.75" customHeight="1">
-      <c r="A71" s="9">
+      <c r="A71" s="12">
         <v>211.0</v>
       </c>
-      <c r="B71" s="8">
+      <c r="B71" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="A72" s="9">
+      <c r="A72" s="12">
         <v>212.0</v>
       </c>
-      <c r="B72" s="8">
+      <c r="B72" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="A73" s="9">
+      <c r="A73" s="12">
         <v>213.0</v>
       </c>
-      <c r="B73" s="8">
+      <c r="B73" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="A74" s="9">
+      <c r="A74" s="12">
         <v>214.0</v>
       </c>
-      <c r="B74" s="8">
+      <c r="B74" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="9">
+      <c r="A75" s="12">
         <v>215.0</v>
       </c>
-      <c r="B75" s="8">
+      <c r="B75" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="A76" s="9">
+      <c r="A76" s="12">
         <v>216.0</v>
       </c>
-      <c r="B76" s="8">
+      <c r="B76" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="A77" s="9">
+      <c r="A77" s="12">
         <v>217.0</v>
       </c>
-      <c r="B77" s="8">
+      <c r="B77" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="78" ht="12.75" customHeight="1">
-      <c r="A78" s="9">
+      <c r="A78" s="12">
         <v>218.0</v>
       </c>
-      <c r="B78" s="8">
+      <c r="B78" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="79" ht="12.75" customHeight="1">
-      <c r="A79" s="9">
+      <c r="A79" s="12">
         <v>219.0</v>
       </c>
-      <c r="B79" s="8">
+      <c r="B79" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="A80" s="9">
+      <c r="A80" s="12">
         <v>220.0</v>
       </c>
-      <c r="B80" s="8">
+      <c r="B80" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="A81" s="9">
+      <c r="A81" s="12">
         <v>221.0</v>
       </c>
-      <c r="B81" s="8">
+      <c r="B81" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="82" ht="12.75" customHeight="1">
-      <c r="A82" s="9">
+      <c r="A82" s="12">
         <v>222.0</v>
       </c>
-      <c r="B82" s="8">
+      <c r="B82" s="11">
         <v>13.0</v>
       </c>
     </row>
     <row r="83" ht="12.75" customHeight="1">
-      <c r="A83" s="8"/>
+      <c r="A83" s="11"/>
     </row>
     <row r="84" ht="12.75" customHeight="1"/>
     <row r="85" ht="12.75" customHeight="1"/>
@@ -3774,109 +3812,109 @@
       <c r="D1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="4">
         <v>0.17</v>
       </c>
     </row>
     <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="2">
+      <c r="A3" s="4">
         <v>2.0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="4">
         <v>0.13</v>
       </c>
     </row>
     <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="2">
+      <c r="A4" s="4">
         <v>3.0</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="4">
         <v>0.16</v>
       </c>
     </row>
     <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="2">
+      <c r="A5" s="4">
         <v>4.0</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="4">
         <v>0.22</v>
       </c>
     </row>
     <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="2">
+      <c r="A6" s="4">
         <v>5.0</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="4">
         <v>0.18</v>
       </c>
     </row>
     <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="2">
+      <c r="A7" s="4">
         <v>6.0</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="4">
         <v>0.14</v>
       </c>
     </row>
@@ -4874,6 +4912,11 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
+  <dataValidations>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" showInputMessage="1" prompt="Suma wag musi wynosić 1" sqref="E1">
+      <formula1>ROUND(SUM(E2:E1000), 2)=1</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
@@ -4900,85 +4943,85 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="7">
         <v>2.0</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="7">
         <v>-0.5</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
+      <c r="E2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
     </row>
     <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="7">
         <v>2.0</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5">
+      <c r="D3" s="7"/>
+      <c r="E3" s="7">
         <v>0.5</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="7">
         <v>0.5</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
     </row>
     <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="7">
         <v>2.0</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5">
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7">
         <v>-0.5</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="7">
         <v>-0.5</v>
       </c>
     </row>
@@ -4989,7 +5032,7 @@
     <row r="9" ht="13.5" customHeight="1"/>
     <row r="10" ht="13.5" customHeight="1"/>
     <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="5"/>
+      <c r="A11" s="7"/>
     </row>
     <row r="12" ht="13.5" customHeight="1"/>
     <row r="13" ht="13.5" customHeight="1"/>
@@ -6001,232 +6044,232 @@
   </cols>
   <sheetData>
     <row r="1" ht="13.5" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="8" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="6">
+      <c r="A2" s="9">
         <v>23.0</v>
       </c>
     </row>
     <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="6">
+      <c r="A3" s="9">
         <v>21.0</v>
       </c>
     </row>
     <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="6">
+      <c r="A4" s="9">
         <v>6.0</v>
       </c>
     </row>
     <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="9">
         <v>17.0</v>
       </c>
     </row>
     <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="6">
+      <c r="A6" s="9">
         <v>8.0</v>
       </c>
     </row>
     <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="6">
+      <c r="A7" s="9">
         <v>30.0</v>
       </c>
     </row>
     <row r="8" ht="13.5" customHeight="1">
-      <c r="A8" s="6">
+      <c r="A8" s="9">
         <v>7.0</v>
       </c>
     </row>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="6">
+      <c r="A9" s="9">
         <v>25.0</v>
       </c>
     </row>
     <row r="10" ht="13.5" customHeight="1">
-      <c r="A10" s="7">
+      <c r="A10" s="10">
         <v>13.0</v>
       </c>
     </row>
     <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="6">
+      <c r="A11" s="9">
         <v>27.0</v>
       </c>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="8">
+      <c r="A12" s="11">
         <v>101.0</v>
       </c>
     </row>
     <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="8">
+      <c r="A13" s="11">
         <v>102.0</v>
       </c>
     </row>
     <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="8">
+      <c r="A14" s="11">
         <v>103.0</v>
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1">
-      <c r="A15" s="8">
+      <c r="A15" s="11">
         <v>104.0</v>
       </c>
     </row>
     <row r="16" ht="13.5" customHeight="1">
-      <c r="A16" s="8">
+      <c r="A16" s="11">
         <v>105.0</v>
       </c>
     </row>
     <row r="17" ht="13.5" customHeight="1">
-      <c r="A17" s="8">
+      <c r="A17" s="11">
         <v>106.0</v>
       </c>
     </row>
     <row r="18" ht="13.5" customHeight="1">
-      <c r="A18" s="8">
+      <c r="A18" s="11">
         <v>107.0</v>
       </c>
     </row>
     <row r="19" ht="13.5" customHeight="1">
-      <c r="A19" s="8">
+      <c r="A19" s="11">
         <v>108.0</v>
       </c>
     </row>
     <row r="20" ht="13.5" customHeight="1">
-      <c r="A20" s="8">
+      <c r="A20" s="11">
         <v>109.0</v>
       </c>
     </row>
     <row r="21" ht="13.5" customHeight="1">
-      <c r="A21" s="8">
+      <c r="A21" s="11">
         <v>110.0</v>
       </c>
     </row>
     <row r="22" ht="13.5" customHeight="1">
-      <c r="A22" s="8">
+      <c r="A22" s="11">
         <v>111.0</v>
       </c>
     </row>
     <row r="23" ht="13.5" customHeight="1">
-      <c r="A23" s="8">
+      <c r="A23" s="11">
         <v>112.0</v>
       </c>
     </row>
     <row r="24" ht="13.5" customHeight="1">
-      <c r="A24" s="9">
+      <c r="A24" s="12">
         <v>201.0</v>
       </c>
     </row>
     <row r="25" ht="13.5" customHeight="1">
-      <c r="A25" s="9">
+      <c r="A25" s="12">
         <v>202.0</v>
       </c>
     </row>
     <row r="26" ht="13.5" customHeight="1">
-      <c r="A26" s="9">
+      <c r="A26" s="12">
         <v>203.0</v>
       </c>
     </row>
     <row r="27" ht="13.5" customHeight="1">
-      <c r="A27" s="9">
+      <c r="A27" s="12">
         <v>204.0</v>
       </c>
     </row>
     <row r="28" ht="13.5" customHeight="1">
-      <c r="A28" s="9">
+      <c r="A28" s="12">
         <v>205.0</v>
       </c>
     </row>
     <row r="29" ht="13.5" customHeight="1">
-      <c r="A29" s="9">
+      <c r="A29" s="12">
         <v>206.0</v>
       </c>
     </row>
     <row r="30" ht="13.5" customHeight="1">
-      <c r="A30" s="9">
+      <c r="A30" s="12">
         <v>207.0</v>
       </c>
     </row>
     <row r="31" ht="13.5" customHeight="1">
-      <c r="A31" s="9">
+      <c r="A31" s="12">
         <v>208.0</v>
       </c>
     </row>
     <row r="32" ht="13.5" customHeight="1">
-      <c r="A32" s="9">
+      <c r="A32" s="12">
         <v>209.0</v>
       </c>
     </row>
     <row r="33" ht="13.5" customHeight="1">
-      <c r="A33" s="9">
+      <c r="A33" s="12">
         <v>210.0</v>
       </c>
     </row>
     <row r="34" ht="13.5" customHeight="1">
-      <c r="A34" s="9">
+      <c r="A34" s="12">
         <v>211.0</v>
       </c>
     </row>
     <row r="35" ht="13.5" customHeight="1">
-      <c r="A35" s="9">
+      <c r="A35" s="12">
         <v>212.0</v>
       </c>
     </row>
     <row r="36" ht="13.5" customHeight="1">
-      <c r="A36" s="9">
+      <c r="A36" s="12">
         <v>213.0</v>
       </c>
     </row>
     <row r="37" ht="13.5" customHeight="1">
-      <c r="A37" s="9">
+      <c r="A37" s="12">
         <v>214.0</v>
       </c>
     </row>
     <row r="38" ht="13.5" customHeight="1">
-      <c r="A38" s="9">
+      <c r="A38" s="12">
         <v>215.0</v>
       </c>
     </row>
     <row r="39" ht="13.5" customHeight="1">
-      <c r="A39" s="9">
+      <c r="A39" s="12">
         <v>216.0</v>
       </c>
     </row>
     <row r="40" ht="13.5" customHeight="1">
-      <c r="A40" s="9">
+      <c r="A40" s="12">
         <v>217.0</v>
       </c>
     </row>
     <row r="41" ht="13.5" customHeight="1">
-      <c r="A41" s="9">
+      <c r="A41" s="12">
         <v>218.0</v>
       </c>
     </row>
     <row r="42" ht="13.5" customHeight="1">
-      <c r="A42" s="9">
+      <c r="A42" s="12">
         <v>219.0</v>
       </c>
     </row>
     <row r="43" ht="13.5" customHeight="1">
-      <c r="A43" s="9">
+      <c r="A43" s="12">
         <v>220.0</v>
       </c>
     </row>
     <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="9">
+      <c r="A44" s="12">
         <v>221.0</v>
       </c>
     </row>
     <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="9">
+      <c r="A45" s="12">
         <v>222.0</v>
       </c>
     </row>
     <row r="46" ht="13.5" customHeight="1">
-      <c r="A46" s="8">
+      <c r="A46" s="11">
         <v>135.0</v>
       </c>
     </row>
@@ -7208,222 +7251,222 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="14" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="6">
+      <c r="A2" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="9">
         <v>23.0</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="11">
         <v>2.0</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="6">
+      <c r="A3" s="9">
         <v>2.0</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="9">
         <v>21.0</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="11">
         <v>2.0</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="6">
+      <c r="A4" s="9">
         <v>3.0</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="9">
         <v>6.0</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="11">
         <v>2.0</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="9">
         <v>4.0</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="9">
         <v>17.0</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="11">
         <v>2.0</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="6">
+      <c r="A6" s="9">
         <v>5.0</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="9">
         <v>8.0</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="11">
         <v>2.0</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="6">
+      <c r="A7" s="9">
         <v>6.0</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="9">
         <v>30.0</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="11">
         <v>2.0</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="6">
+      <c r="A8" s="9">
         <v>7.0</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="9">
         <v>7.0</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="11">
         <v>2.0</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="6">
+      <c r="A9" s="9">
         <v>8.0</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="9">
         <v>25.0</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="11">
         <v>2.0</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="6">
+      <c r="A10" s="9">
         <v>9.0</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="10">
         <v>13.0</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="11">
         <v>2.0</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="6">
+      <c r="A11" s="9">
         <v>10.0</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="9">
         <v>27.0</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="11">
         <v>2.0</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="17">
         <v>1.0</v>
       </c>
     </row>
@@ -7448,571 +7491,571 @@
     <row r="30" ht="12.75" customHeight="1"/>
     <row r="31" ht="12.75" customHeight="1"/>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="D32" s="3"/>
+      <c r="D32" s="5"/>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="D33" s="3"/>
+      <c r="D33" s="5"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="D34" s="3"/>
+      <c r="D34" s="5"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="D35" s="3"/>
+      <c r="D35" s="5"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="D36" s="3"/>
+      <c r="D36" s="5"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="D37" s="3"/>
+      <c r="D37" s="5"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="D38" s="3"/>
+      <c r="D38" s="5"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="D39" s="3"/>
+      <c r="D39" s="5"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="D40" s="3"/>
+      <c r="D40" s="5"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="D41" s="3"/>
+      <c r="D41" s="5"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="D42" s="3"/>
+      <c r="D42" s="5"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
-      <c r="D43" s="3"/>
+      <c r="D43" s="5"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="D44" s="3"/>
+      <c r="D44" s="5"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="D45" s="3"/>
+      <c r="D45" s="5"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="D46" s="3"/>
+      <c r="D46" s="5"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="D47" s="3"/>
+      <c r="D47" s="5"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="D48" s="3"/>
+      <c r="D48" s="5"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="D49" s="3"/>
+      <c r="D49" s="5"/>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="D50" s="3"/>
+      <c r="D50" s="5"/>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="D51" s="3"/>
+      <c r="D51" s="5"/>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="D52" s="3"/>
+      <c r="D52" s="5"/>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="D53" s="3"/>
+      <c r="D53" s="5"/>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="D54" s="3"/>
+      <c r="D54" s="5"/>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="D55" s="3"/>
+      <c r="D55" s="5"/>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="D56" s="3"/>
+      <c r="D56" s="5"/>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="D57" s="3"/>
+      <c r="D57" s="5"/>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="D58" s="3"/>
+      <c r="D58" s="5"/>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="D59" s="3"/>
+      <c r="D59" s="5"/>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="D60" s="3"/>
+      <c r="D60" s="5"/>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="D61" s="3"/>
+      <c r="D61" s="5"/>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="D62" s="3"/>
+      <c r="D62" s="5"/>
     </row>
     <row r="63" ht="12.75" customHeight="1">
-      <c r="D63" s="3"/>
+      <c r="D63" s="5"/>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="D64" s="3"/>
+      <c r="D64" s="5"/>
     </row>
     <row r="65" ht="12.75" customHeight="1">
-      <c r="D65" s="3"/>
+      <c r="D65" s="5"/>
     </row>
     <row r="66" ht="12.75" customHeight="1">
-      <c r="D66" s="3"/>
+      <c r="D66" s="5"/>
     </row>
     <row r="67" ht="12.75" customHeight="1">
-      <c r="D67" s="3"/>
+      <c r="D67" s="5"/>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="D68" s="3"/>
+      <c r="D68" s="5"/>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="D69" s="3"/>
+      <c r="D69" s="5"/>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="D70" s="3"/>
+      <c r="D70" s="5"/>
     </row>
     <row r="71" ht="12.75" customHeight="1">
-      <c r="D71" s="3"/>
+      <c r="D71" s="5"/>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="D72" s="3"/>
+      <c r="D72" s="5"/>
     </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="D73" s="3"/>
+      <c r="D73" s="5"/>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="D74" s="3"/>
+      <c r="D74" s="5"/>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="D75" s="3"/>
+      <c r="D75" s="5"/>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="D76" s="3"/>
+      <c r="D76" s="5"/>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="D77" s="3"/>
+      <c r="D77" s="5"/>
     </row>
     <row r="78" ht="12.75" customHeight="1">
-      <c r="D78" s="3"/>
+      <c r="D78" s="5"/>
     </row>
     <row r="79" ht="12.75" customHeight="1">
-      <c r="D79" s="3"/>
+      <c r="D79" s="5"/>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="D80" s="3"/>
+      <c r="D80" s="5"/>
     </row>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="D81" s="3"/>
+      <c r="D81" s="5"/>
     </row>
     <row r="82" ht="12.75" customHeight="1">
-      <c r="D82" s="3"/>
+      <c r="D82" s="5"/>
     </row>
     <row r="83" ht="12.75" customHeight="1">
-      <c r="D83" s="3"/>
+      <c r="D83" s="5"/>
     </row>
     <row r="84" ht="12.75" customHeight="1">
-      <c r="D84" s="3"/>
+      <c r="D84" s="5"/>
     </row>
     <row r="85" ht="12.75" customHeight="1">
-      <c r="D85" s="3"/>
+      <c r="D85" s="5"/>
     </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="D86" s="3"/>
+      <c r="D86" s="5"/>
     </row>
     <row r="87" ht="12.75" customHeight="1">
-      <c r="D87" s="3"/>
+      <c r="D87" s="5"/>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="D88" s="3"/>
+      <c r="D88" s="5"/>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="D89" s="3"/>
+      <c r="D89" s="5"/>
     </row>
     <row r="90" ht="12.75" customHeight="1">
-      <c r="D90" s="3"/>
+      <c r="D90" s="5"/>
     </row>
     <row r="91" ht="12.75" customHeight="1">
-      <c r="D91" s="3"/>
+      <c r="D91" s="5"/>
     </row>
     <row r="92" ht="12.75" customHeight="1">
-      <c r="D92" s="3"/>
+      <c r="D92" s="5"/>
     </row>
     <row r="93" ht="12.75" customHeight="1">
-      <c r="D93" s="3"/>
+      <c r="D93" s="5"/>
     </row>
     <row r="94" ht="12.75" customHeight="1">
-      <c r="D94" s="3"/>
+      <c r="D94" s="5"/>
     </row>
     <row r="95" ht="12.75" customHeight="1">
-      <c r="D95" s="3"/>
+      <c r="D95" s="5"/>
     </row>
     <row r="96" ht="12.75" customHeight="1">
-      <c r="D96" s="3"/>
+      <c r="D96" s="5"/>
     </row>
     <row r="97" ht="12.75" customHeight="1">
-      <c r="D97" s="3"/>
+      <c r="D97" s="5"/>
     </row>
     <row r="98" ht="12.75" customHeight="1">
-      <c r="D98" s="3"/>
+      <c r="D98" s="5"/>
     </row>
     <row r="99" ht="12.75" customHeight="1">
-      <c r="D99" s="3"/>
+      <c r="D99" s="5"/>
     </row>
     <row r="100" ht="12.75" customHeight="1">
-      <c r="D100" s="3"/>
+      <c r="D100" s="5"/>
     </row>
     <row r="101" ht="12.75" customHeight="1">
-      <c r="D101" s="3"/>
+      <c r="D101" s="5"/>
     </row>
     <row r="102" ht="12.75" customHeight="1">
-      <c r="D102" s="3"/>
+      <c r="D102" s="5"/>
     </row>
     <row r="103" ht="12.75" customHeight="1">
-      <c r="D103" s="3"/>
+      <c r="D103" s="5"/>
     </row>
     <row r="104" ht="12.75" customHeight="1">
-      <c r="D104" s="3"/>
+      <c r="D104" s="5"/>
     </row>
     <row r="105" ht="12.75" customHeight="1">
-      <c r="D105" s="3"/>
+      <c r="D105" s="5"/>
     </row>
     <row r="106" ht="12.75" customHeight="1">
-      <c r="D106" s="3"/>
+      <c r="D106" s="5"/>
     </row>
     <row r="107" ht="12.75" customHeight="1">
-      <c r="D107" s="3"/>
+      <c r="D107" s="5"/>
     </row>
     <row r="108" ht="12.75" customHeight="1">
-      <c r="D108" s="3"/>
+      <c r="D108" s="5"/>
     </row>
     <row r="109" ht="12.75" customHeight="1">
-      <c r="D109" s="3"/>
+      <c r="D109" s="5"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
-      <c r="D110" s="3"/>
+      <c r="D110" s="5"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
-      <c r="D111" s="3"/>
+      <c r="D111" s="5"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
-      <c r="D112" s="3"/>
+      <c r="D112" s="5"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
-      <c r="D113" s="3"/>
+      <c r="D113" s="5"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
-      <c r="D114" s="3"/>
+      <c r="D114" s="5"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
-      <c r="D115" s="3"/>
+      <c r="D115" s="5"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
-      <c r="D116" s="3"/>
+      <c r="D116" s="5"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
-      <c r="D117" s="3"/>
+      <c r="D117" s="5"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
-      <c r="D118" s="3"/>
+      <c r="D118" s="5"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
-      <c r="D119" s="3"/>
+      <c r="D119" s="5"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
-      <c r="D120" s="3"/>
+      <c r="D120" s="5"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
-      <c r="D121" s="3"/>
+      <c r="D121" s="5"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
-      <c r="D122" s="3"/>
+      <c r="D122" s="5"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
-      <c r="D123" s="3"/>
+      <c r="D123" s="5"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
-      <c r="D124" s="3"/>
+      <c r="D124" s="5"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
-      <c r="D125" s="3"/>
+      <c r="D125" s="5"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
-      <c r="D126" s="3"/>
+      <c r="D126" s="5"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
-      <c r="D127" s="3"/>
+      <c r="D127" s="5"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
-      <c r="D128" s="3"/>
+      <c r="D128" s="5"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
-      <c r="D129" s="3"/>
+      <c r="D129" s="5"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
-      <c r="D130" s="3"/>
+      <c r="D130" s="5"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
-      <c r="D131" s="3"/>
+      <c r="D131" s="5"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
-      <c r="D132" s="3"/>
+      <c r="D132" s="5"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
-      <c r="D133" s="3"/>
+      <c r="D133" s="5"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
-      <c r="D134" s="3"/>
+      <c r="D134" s="5"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
-      <c r="D135" s="3"/>
+      <c r="D135" s="5"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
-      <c r="D136" s="3"/>
+      <c r="D136" s="5"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
-      <c r="D137" s="3"/>
+      <c r="D137" s="5"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
-      <c r="D138" s="3"/>
+      <c r="D138" s="5"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
-      <c r="D139" s="3"/>
+      <c r="D139" s="5"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
-      <c r="D140" s="3"/>
+      <c r="D140" s="5"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
-      <c r="D141" s="3"/>
+      <c r="D141" s="5"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
-      <c r="D142" s="3"/>
+      <c r="D142" s="5"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
-      <c r="D143" s="3"/>
+      <c r="D143" s="5"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
-      <c r="D144" s="3"/>
+      <c r="D144" s="5"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
-      <c r="D145" s="3"/>
+      <c r="D145" s="5"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
-      <c r="D146" s="3"/>
+      <c r="D146" s="5"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
-      <c r="D147" s="3"/>
+      <c r="D147" s="5"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
-      <c r="D148" s="3"/>
+      <c r="D148" s="5"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
-      <c r="D149" s="3"/>
+      <c r="D149" s="5"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
-      <c r="D150" s="3"/>
+      <c r="D150" s="5"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
-      <c r="D151" s="3"/>
+      <c r="D151" s="5"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
-      <c r="D152" s="3"/>
+      <c r="D152" s="5"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
-      <c r="D153" s="3"/>
+      <c r="D153" s="5"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
-      <c r="D154" s="3"/>
+      <c r="D154" s="5"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
-      <c r="D155" s="3"/>
+      <c r="D155" s="5"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
-      <c r="D156" s="3"/>
+      <c r="D156" s="5"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
-      <c r="D157" s="3"/>
+      <c r="D157" s="5"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
-      <c r="D158" s="3"/>
+      <c r="D158" s="5"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
-      <c r="D159" s="3"/>
+      <c r="D159" s="5"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
-      <c r="D160" s="3"/>
+      <c r="D160" s="5"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
-      <c r="D161" s="3"/>
+      <c r="D161" s="5"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
-      <c r="D162" s="3"/>
+      <c r="D162" s="5"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
-      <c r="D163" s="3"/>
+      <c r="D163" s="5"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
-      <c r="D164" s="3"/>
+      <c r="D164" s="5"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
-      <c r="D165" s="3"/>
+      <c r="D165" s="5"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
-      <c r="D166" s="3"/>
+      <c r="D166" s="5"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
-      <c r="D167" s="3"/>
+      <c r="D167" s="5"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
-      <c r="D168" s="3"/>
+      <c r="D168" s="5"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
-      <c r="D169" s="3"/>
+      <c r="D169" s="5"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
-      <c r="D170" s="3"/>
+      <c r="D170" s="5"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
-      <c r="D171" s="3"/>
+      <c r="D171" s="5"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
-      <c r="D172" s="3"/>
+      <c r="D172" s="5"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
-      <c r="D173" s="3"/>
+      <c r="D173" s="5"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
-      <c r="D174" s="3"/>
+      <c r="D174" s="5"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
-      <c r="D175" s="3"/>
+      <c r="D175" s="5"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
-      <c r="D176" s="3"/>
+      <c r="D176" s="5"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
-      <c r="D177" s="3"/>
+      <c r="D177" s="5"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
-      <c r="D178" s="3"/>
+      <c r="D178" s="5"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
-      <c r="D179" s="3"/>
+      <c r="D179" s="5"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
-      <c r="D180" s="3"/>
+      <c r="D180" s="5"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
-      <c r="D181" s="3"/>
+      <c r="D181" s="5"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
-      <c r="D182" s="3"/>
+      <c r="D182" s="5"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
-      <c r="D183" s="3"/>
+      <c r="D183" s="5"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
-      <c r="D184" s="3"/>
+      <c r="D184" s="5"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
-      <c r="D185" s="3"/>
+      <c r="D185" s="5"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
-      <c r="D186" s="3"/>
+      <c r="D186" s="5"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
-      <c r="D187" s="3"/>
+      <c r="D187" s="5"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
-      <c r="D188" s="3"/>
+      <c r="D188" s="5"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
-      <c r="D189" s="3"/>
+      <c r="D189" s="5"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
-      <c r="D190" s="3"/>
+      <c r="D190" s="5"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
-      <c r="D191" s="3"/>
+      <c r="D191" s="5"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
-      <c r="D192" s="3"/>
+      <c r="D192" s="5"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
-      <c r="D193" s="3"/>
+      <c r="D193" s="5"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
-      <c r="D194" s="3"/>
+      <c r="D194" s="5"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
-      <c r="D195" s="3"/>
+      <c r="D195" s="5"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
-      <c r="D196" s="3"/>
+      <c r="D196" s="5"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
-      <c r="D197" s="3"/>
+      <c r="D197" s="5"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
-      <c r="D198" s="3"/>
+      <c r="D198" s="5"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
-      <c r="D199" s="3"/>
+      <c r="D199" s="5"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
-      <c r="D200" s="3"/>
+      <c r="D200" s="5"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
-      <c r="D201" s="3"/>
+      <c r="D201" s="5"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
-      <c r="D202" s="3"/>
+      <c r="D202" s="5"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
-      <c r="D203" s="3"/>
+      <c r="D203" s="5"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
-      <c r="D204" s="3"/>
+      <c r="D204" s="5"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
-      <c r="D205" s="3"/>
+      <c r="D205" s="5"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
-      <c r="D206" s="3"/>
+      <c r="D206" s="5"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
-      <c r="D207" s="3"/>
+      <c r="D207" s="5"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
-      <c r="D208" s="3"/>
+      <c r="D208" s="5"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
-      <c r="D209" s="3"/>
+      <c r="D209" s="5"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
-      <c r="D210" s="3"/>
+      <c r="D210" s="5"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
-      <c r="D211" s="3"/>
+      <c r="D211" s="5"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
-      <c r="D212" s="3"/>
+      <c r="D212" s="5"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
-      <c r="D213" s="3"/>
+      <c r="D213" s="5"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
-      <c r="D214" s="3"/>
+      <c r="D214" s="5"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
-      <c r="D215" s="3"/>
+      <c r="D215" s="5"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
-      <c r="D216" s="3"/>
+      <c r="D216" s="5"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
-      <c r="D217" s="3"/>
+      <c r="D217" s="5"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
-      <c r="D218" s="3"/>
+      <c r="D218" s="5"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
-      <c r="D219" s="3"/>
+      <c r="D219" s="5"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
-      <c r="D220" s="3"/>
+      <c r="D220" s="5"/>
     </row>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1"/>
@@ -8819,240 +8862,240 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="19" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9">
+      <c r="A2" s="12">
         <v>101.0</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="21">
         <v>20.0</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9">
+      <c r="A3" s="12">
         <v>102.0</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="21">
         <v>8.0</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9">
+      <c r="A4" s="12">
         <v>103.0</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="21">
         <v>8.0</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="12">
         <v>104.0</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="21">
         <v>7.0</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9">
+      <c r="A6" s="12">
         <v>105.0</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="21">
         <v>6.0</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9">
+      <c r="A7" s="12">
         <v>106.0</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="21">
         <v>12.0</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9">
+      <c r="A8" s="12">
         <v>107.0</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="21">
         <v>7.0</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9">
+      <c r="A9" s="12">
         <v>108.0</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="21">
         <v>12.0</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9">
+      <c r="A10" s="12">
         <v>109.0</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="21">
         <v>7.0</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9">
+      <c r="A11" s="12">
         <v>110.0</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="21">
         <v>8.0</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9">
+      <c r="A12" s="12">
         <v>111.0</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="21">
         <v>8.0</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9">
+      <c r="A13" s="12">
         <v>112.0</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="11">
         <v>8.0</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8">
+      <c r="A14" s="11">
         <v>135.0</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="11">
         <v>8.0</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="11">
         <v>1.0</v>
       </c>
     </row>
@@ -9143,346 +9186,346 @@
     <row r="105" ht="15.75" customHeight="1"/>
     <row r="106" ht="15.75" customHeight="1"/>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="D107" s="17"/>
+      <c r="D107" s="22"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="D108" s="17"/>
+      <c r="D108" s="22"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="D109" s="17"/>
+      <c r="D109" s="22"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="D110" s="17"/>
+      <c r="D110" s="22"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="D111" s="17"/>
+      <c r="D111" s="22"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="D112" s="17"/>
+      <c r="D112" s="22"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="D113" s="17"/>
+      <c r="D113" s="22"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="D114" s="17"/>
+      <c r="D114" s="22"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="D115" s="17"/>
+      <c r="D115" s="22"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="D116" s="17"/>
+      <c r="D116" s="22"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="D117" s="17"/>
+      <c r="D117" s="22"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="D118" s="17"/>
+      <c r="D118" s="22"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="D119" s="17"/>
+      <c r="D119" s="22"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="D120" s="17"/>
+      <c r="D120" s="22"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="D121" s="17"/>
+      <c r="D121" s="22"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="D122" s="17"/>
+      <c r="D122" s="22"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="D123" s="17"/>
+      <c r="D123" s="22"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="D124" s="17"/>
+      <c r="D124" s="22"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="D125" s="17"/>
+      <c r="D125" s="22"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="D126" s="17"/>
+      <c r="D126" s="22"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="D127" s="17"/>
+      <c r="D127" s="22"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="D128" s="17"/>
+      <c r="D128" s="22"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="D129" s="17"/>
+      <c r="D129" s="22"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="D130" s="17"/>
+      <c r="D130" s="22"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="D131" s="17"/>
+      <c r="D131" s="22"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="D132" s="17"/>
+      <c r="D132" s="22"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="D133" s="17"/>
+      <c r="D133" s="22"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="D134" s="17"/>
+      <c r="D134" s="22"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="D135" s="17"/>
+      <c r="D135" s="22"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="D136" s="17"/>
+      <c r="D136" s="22"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="D137" s="17"/>
+      <c r="D137" s="22"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="D138" s="17"/>
+      <c r="D138" s="22"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="D139" s="17"/>
+      <c r="D139" s="22"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="D140" s="17"/>
+      <c r="D140" s="22"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="D141" s="17"/>
+      <c r="D141" s="22"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="D142" s="17"/>
+      <c r="D142" s="22"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="D143" s="17"/>
+      <c r="D143" s="22"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="D144" s="17"/>
+      <c r="D144" s="22"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="D145" s="17"/>
+      <c r="D145" s="22"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="D146" s="17"/>
+      <c r="D146" s="22"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="D147" s="17"/>
+      <c r="D147" s="22"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="D148" s="17"/>
+      <c r="D148" s="22"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="D149" s="17"/>
+      <c r="D149" s="22"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="D150" s="17"/>
+      <c r="D150" s="22"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="D151" s="17"/>
+      <c r="D151" s="22"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="D152" s="17"/>
+      <c r="D152" s="22"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="D153" s="17"/>
+      <c r="D153" s="22"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="D154" s="17"/>
+      <c r="D154" s="22"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="D155" s="17"/>
+      <c r="D155" s="22"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="D156" s="17"/>
+      <c r="D156" s="22"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="D157" s="17"/>
+      <c r="D157" s="22"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="D158" s="17"/>
+      <c r="D158" s="22"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="D159" s="17"/>
+      <c r="D159" s="22"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="D160" s="17"/>
+      <c r="D160" s="22"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="D161" s="17"/>
+      <c r="D161" s="22"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="D162" s="17"/>
+      <c r="D162" s="22"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="D163" s="17"/>
+      <c r="D163" s="22"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="D164" s="17"/>
+      <c r="D164" s="22"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="D165" s="17"/>
+      <c r="D165" s="22"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="D166" s="17"/>
+      <c r="D166" s="22"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="D167" s="17"/>
+      <c r="D167" s="22"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="D168" s="17"/>
+      <c r="D168" s="22"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="D169" s="17"/>
+      <c r="D169" s="22"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="D170" s="17"/>
+      <c r="D170" s="22"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="D171" s="17"/>
+      <c r="D171" s="22"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="D172" s="17"/>
+      <c r="D172" s="22"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="D173" s="17"/>
+      <c r="D173" s="22"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="D174" s="17"/>
+      <c r="D174" s="22"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="D175" s="17"/>
+      <c r="D175" s="22"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="D176" s="17"/>
+      <c r="D176" s="22"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="D177" s="17"/>
+      <c r="D177" s="22"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="D178" s="17"/>
+      <c r="D178" s="22"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="D179" s="17"/>
+      <c r="D179" s="22"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="D180" s="17"/>
+      <c r="D180" s="22"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="D181" s="17"/>
+      <c r="D181" s="22"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="D182" s="17"/>
+      <c r="D182" s="22"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="D183" s="17"/>
+      <c r="D183" s="22"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="D184" s="17"/>
+      <c r="D184" s="22"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="D185" s="17"/>
+      <c r="D185" s="22"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="D186" s="17"/>
+      <c r="D186" s="22"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="D187" s="17"/>
+      <c r="D187" s="22"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="D188" s="17"/>
+      <c r="D188" s="22"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="D189" s="17"/>
+      <c r="D189" s="22"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="D190" s="17"/>
+      <c r="D190" s="22"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="D191" s="17"/>
+      <c r="D191" s="22"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="D192" s="17"/>
+      <c r="D192" s="22"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="D193" s="17"/>
+      <c r="D193" s="22"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="D194" s="17"/>
+      <c r="D194" s="22"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="D195" s="17"/>
+      <c r="D195" s="22"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="D196" s="17"/>
+      <c r="D196" s="22"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="D197" s="17"/>
+      <c r="D197" s="22"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="D198" s="17"/>
+      <c r="D198" s="22"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="D199" s="17"/>
+      <c r="D199" s="22"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="D200" s="17"/>
+      <c r="D200" s="22"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="D201" s="17"/>
+      <c r="D201" s="22"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="D202" s="17"/>
+      <c r="D202" s="22"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="D203" s="17"/>
+      <c r="D203" s="22"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="D204" s="17"/>
+      <c r="D204" s="22"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="D205" s="17"/>
+      <c r="D205" s="22"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="D206" s="17"/>
+      <c r="D206" s="22"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="D207" s="17"/>
+      <c r="D207" s="22"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="D208" s="17"/>
+      <c r="D208" s="22"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="D209" s="17"/>
+      <c r="D209" s="22"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="D210" s="17"/>
+      <c r="D210" s="22"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="D211" s="17"/>
+      <c r="D211" s="22"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="D212" s="17"/>
+      <c r="D212" s="22"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="D213" s="17"/>
+      <c r="D213" s="22"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="D214" s="17"/>
+      <c r="D214" s="22"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="D215" s="17"/>
+      <c r="D215" s="22"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="D216" s="17"/>
+      <c r="D216" s="22"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="D217" s="17"/>
+      <c r="D217" s="22"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="D218" s="17"/>
+      <c r="D218" s="22"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="D219" s="17"/>
+      <c r="D219" s="22"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="D220" s="17"/>
+      <c r="D220" s="22"/>
     </row>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1"/>
@@ -10280,402 +10323,402 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="6.57"/>
-    <col customWidth="1" min="2" max="2" width="26.86"/>
-    <col customWidth="1" min="3" max="3" width="64.0"/>
-    <col customWidth="1" min="4" max="4" width="65.57"/>
-    <col customWidth="1" min="5" max="5" width="19.14"/>
+    <col customWidth="1" min="2" max="2" width="54.57"/>
+    <col customWidth="1" min="3" max="3" width="149.71"/>
+    <col customWidth="1" min="4" max="4" width="20.43"/>
+    <col customWidth="1" min="5" max="5" width="27.57"/>
     <col customWidth="1" min="6" max="6" width="13.86"/>
     <col customWidth="1" min="7" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.5" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="19" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="9">
+      <c r="A2" s="12">
         <v>201.0</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="11">
         <v>0.5</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="9">
+      <c r="A3" s="12">
         <v>202.0</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="11">
         <v>0.5</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="9">
+      <c r="A4" s="12">
         <v>203.0</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="11">
         <v>0.5</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="9">
+      <c r="A5" s="12">
         <v>204.0</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="E5" s="8">
+      <c r="D5" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="E5" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="9">
+      <c r="A6" s="12">
         <v>205.0</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="11">
         <v>0.5</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="9">
+      <c r="A7" s="12">
         <v>206.0</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="11">
         <v>0.5</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="8" ht="13.5" customHeight="1">
-      <c r="A8" s="9">
+      <c r="A8" s="12">
         <v>207.0</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="11">
         <v>0.1</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="9">
+      <c r="A9" s="12">
         <v>208.0</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="11">
         <v>0.1</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="10" ht="13.5" customHeight="1">
-      <c r="A10" s="9">
+      <c r="A10" s="12">
         <v>209.0</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="11">
         <v>0.1</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="9">
+      <c r="A11" s="12">
         <v>210.0</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="11">
         <v>0.1</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="9">
+      <c r="A12" s="12">
         <v>211.0</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="11">
         <v>0.1</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="9">
+      <c r="A13" s="12">
         <v>212.0</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="11">
         <v>0.1</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="9">
+      <c r="A14" s="12">
         <v>213.0</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="D14" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="D14" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="E14" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1">
-      <c r="A15" s="9">
+      <c r="A15" s="12">
         <v>214.0</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="11">
         <v>1.5</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="16" ht="13.5" customHeight="1">
-      <c r="A16" s="9">
+      <c r="A16" s="12">
         <v>215.0</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="11">
         <v>0.5</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="17" ht="13.5" customHeight="1">
-      <c r="A17" s="9">
+      <c r="A17" s="12">
         <v>216.0</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="11">
         <v>0.5</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="18" ht="13.5" customHeight="1">
-      <c r="A18" s="9">
+      <c r="A18" s="12">
         <v>217.0</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="D18" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="E18" s="8">
+      <c r="D18" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="E18" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="19" ht="13.5" customHeight="1">
-      <c r="A19" s="9">
+      <c r="A19" s="12">
         <v>218.0</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="11">
         <v>0.5</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="20" ht="13.5" customHeight="1">
-      <c r="A20" s="9">
+      <c r="A20" s="12">
         <v>219.0</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="11">
         <v>3.0</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="21" ht="13.5" customHeight="1">
-      <c r="A21" s="9">
+      <c r="A21" s="12">
         <v>220.0</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="11">
         <v>3.0</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="22" ht="13.5" customHeight="1">
-      <c r="A22" s="9">
+      <c r="A22" s="12">
         <v>221.0</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="11">
         <v>3.0</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="11">
         <v>1.0</v>
       </c>
     </row>
     <row r="23" ht="13.5" customHeight="1">
-      <c r="A23" s="9">
+      <c r="A23" s="12">
         <v>222.0</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="11">
         <v>3.0</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="11">
         <v>1.0</v>
       </c>
     </row>
@@ -11680,261 +11723,261 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="17" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="8">
+      <c r="A2" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="11">
         <v>23.0</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="11" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="10">
+      <c r="A3" s="17">
         <v>2.0</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="11">
         <v>21.0</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="17" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="10">
+      <c r="A4" s="17">
         <v>3.0</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="11">
         <v>21.0</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="17" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="10">
+      <c r="A5" s="17">
         <v>4.0</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="11">
         <v>6.0</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="11" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="10">
+      <c r="A6" s="17">
         <v>5.0</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="11">
         <v>6.0</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="11" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="10">
+      <c r="A7" s="17">
         <v>6.0</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="26">
         <v>17.0</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="11" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="10">
+      <c r="A8" s="17">
         <v>7.0</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="11">
         <v>17.0</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="11" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="10">
+      <c r="A9" s="17">
         <v>8.0</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="11">
         <v>8.0</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="17" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="10">
+      <c r="A10" s="17">
         <v>9.0</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="11">
         <v>8.0</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="17" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="10">
+      <c r="A11" s="17">
         <v>10.0</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="26">
         <v>30.0</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="11" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="10">
+      <c r="A12" s="17">
         <v>11.0</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="11">
         <v>30.0</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="11" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="10">
+      <c r="A13" s="17">
         <v>12.0</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="11">
         <v>13.0</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="11" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="10">
+      <c r="A14" s="17">
         <v>13.0</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="11">
         <v>13.0</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="11" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="10">
+      <c r="A15" s="17">
         <v>14.0</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="11">
         <v>25.0</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="17" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="10">
+      <c r="A16" s="17">
         <v>15.0</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="11">
         <v>25.0</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="17" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="10">
+      <c r="A17" s="17">
         <v>16.0</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="11">
         <v>27.0</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="17" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="10">
+      <c r="A18" s="17">
         <v>17.0</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="11">
         <v>27.0</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="17" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
-      <c r="A19" s="10">
+      <c r="A19" s="17">
         <v>18.0</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="11">
         <v>7.0</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="11" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="A20" s="10">
+      <c r="A20" s="17">
         <v>19.0</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="11">
         <v>7.0</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="11" t="s">
         <v>179</v>
       </c>
     </row>
@@ -12938,1410 +12981,1412 @@
     <col customWidth="1" min="3" max="3" width="10.14"/>
     <col customWidth="1" min="4" max="4" width="9.43"/>
     <col customWidth="1" min="5" max="5" width="11.0"/>
-    <col customWidth="1" min="6" max="11" width="8.71"/>
+    <col customWidth="1" min="6" max="6" width="11.71"/>
+    <col customWidth="1" min="7" max="7" width="11.57"/>
+    <col customWidth="1" min="8" max="11" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="28" t="s">
         <v>69</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>194</v>
+      <c r="F1" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="6">
+      <c r="A2" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="9">
         <v>23.0</v>
       </c>
-      <c r="C2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D2" s="16">
+      <c r="C2" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D2" s="21">
         <v>80.0</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="21">
         <v>80.0</v>
       </c>
-      <c r="F2" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G2" s="10">
+      <c r="F2" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G2" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="10">
+      <c r="A3" s="17">
         <v>2.0</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="9">
         <v>23.0</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="4">
         <v>2.0</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="21">
         <v>50.0</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="21">
         <v>50.0</v>
       </c>
-      <c r="F3" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G3" s="10">
+      <c r="F3" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G3" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="10">
+      <c r="A4" s="17">
         <v>3.0</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="9">
         <v>23.0</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="4">
         <v>3.0</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="21">
         <v>70.0</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="21">
         <v>70.0</v>
       </c>
-      <c r="F4" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G4" s="10">
+      <c r="F4" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G4" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="10">
+      <c r="A5" s="17">
         <v>4.0</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="9">
         <v>23.0</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="4">
         <v>4.0</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="21">
         <v>50.0</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="21">
         <v>50.0</v>
       </c>
-      <c r="F5" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G5" s="10">
+      <c r="F5" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G5" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="10">
+      <c r="A6" s="17">
         <v>5.0</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="9">
         <v>23.0</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="4">
         <v>5.0</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="21">
         <v>40.0</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="21">
         <v>40.0</v>
       </c>
-      <c r="F6" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G6" s="10">
+      <c r="F6" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G6" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="10">
+      <c r="A7" s="17">
         <v>6.0</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="9">
         <v>23.0</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="4">
         <v>6.0</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="21">
         <v>30.0</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="21">
         <v>30.0</v>
       </c>
-      <c r="F7" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G7" s="10">
+      <c r="F7" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G7" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="10">
+      <c r="A8" s="17">
         <v>7.0</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="9">
         <v>6.0</v>
       </c>
-      <c r="C8" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D8" s="16">
+      <c r="C8" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D8" s="21">
         <v>30.0</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="21">
         <v>30.0</v>
       </c>
-      <c r="F8" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G8" s="10">
+      <c r="F8" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G8" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="10">
+      <c r="A9" s="17">
         <v>8.0</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="9">
         <v>6.0</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="4">
         <v>2.0</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="21">
         <v>80.0</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="21">
         <v>80.0</v>
       </c>
-      <c r="F9" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G9" s="10">
+      <c r="F9" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G9" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="10">
+      <c r="A10" s="17">
         <v>9.0</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="9">
         <v>6.0</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="4">
         <v>3.0</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="21">
         <v>30.0</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="21">
         <v>30.0</v>
       </c>
-      <c r="F10" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G10" s="10">
+      <c r="F10" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G10" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="10">
+      <c r="A11" s="17">
         <v>10.0</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="9">
         <v>6.0</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="4">
         <v>4.0</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="21">
         <v>50.0</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="21">
         <v>50.0</v>
       </c>
-      <c r="F11" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G11" s="10">
+      <c r="F11" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G11" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="10">
+      <c r="A12" s="17">
         <v>11.0</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="9">
         <v>6.0</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="4">
         <v>5.0</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="21">
         <v>40.0</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="21">
         <v>40.0</v>
       </c>
-      <c r="F12" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G12" s="10">
+      <c r="F12" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G12" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="10">
+      <c r="A13" s="17">
         <v>12.0</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="9">
         <v>6.0</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="4">
         <v>6.0</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="21">
         <v>40.0</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="21">
         <v>40.0</v>
       </c>
-      <c r="F13" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G13" s="10">
+      <c r="F13" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G13" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="10">
+      <c r="A14" s="17">
         <v>13.0</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="9">
         <v>17.0</v>
       </c>
-      <c r="C14" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D14" s="16">
+      <c r="C14" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="21">
         <v>90.0</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="21">
         <v>90.0</v>
       </c>
-      <c r="F14" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G14" s="10">
+      <c r="F14" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G14" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="10">
+      <c r="A15" s="17">
         <v>14.0</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="9">
         <v>17.0</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="4">
         <v>2.0</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="21">
         <v>20.0</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="21">
         <v>20.0</v>
       </c>
-      <c r="F15" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G15" s="10">
+      <c r="F15" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G15" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="10">
+      <c r="A16" s="17">
         <v>15.0</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="9">
         <v>17.0</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="4">
         <v>3.0</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="21">
         <v>40.0</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="21">
         <v>40.0</v>
       </c>
-      <c r="F16" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G16" s="10">
+      <c r="F16" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G16" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="10">
+      <c r="A17" s="17">
         <v>16.0</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="9">
         <v>17.0</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="4">
         <v>4.0</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="21">
         <v>60.0</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="21">
         <v>60.0</v>
       </c>
-      <c r="F17" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G17" s="10">
+      <c r="F17" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G17" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="10">
+      <c r="A18" s="17">
         <v>17.0</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="9">
         <v>17.0</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="4">
         <v>5.0</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="21">
         <v>40.0</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="21">
         <v>40.0</v>
       </c>
-      <c r="F18" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G18" s="10">
+      <c r="F18" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G18" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
-      <c r="A19" s="10">
+      <c r="A19" s="17">
         <v>18.0</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="9">
         <v>17.0</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="4">
         <v>6.0</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="21">
         <v>20.0</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="21">
         <v>20.0</v>
       </c>
-      <c r="F19" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G19" s="10">
+      <c r="F19" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G19" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="A20" s="10">
+      <c r="A20" s="17">
         <v>19.0</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="9">
         <v>21.0</v>
       </c>
-      <c r="C20" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D20" s="16">
+      <c r="C20" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D20" s="21">
         <v>60.0</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="21">
         <v>60.0</v>
       </c>
-      <c r="F20" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G20" s="10">
+      <c r="F20" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G20" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="21" ht="12.75" customHeight="1">
-      <c r="A21" s="10">
+      <c r="A21" s="17">
         <v>20.0</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="9">
         <v>21.0</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="4">
         <v>2.0</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="21">
         <v>30.0</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="21">
         <v>30.0</v>
       </c>
-      <c r="F21" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G21" s="10">
+      <c r="F21" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G21" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
-      <c r="A22" s="10">
+      <c r="A22" s="17">
         <v>21.0</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="9">
         <v>21.0</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="4">
         <v>3.0</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="21">
         <v>50.0</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="21">
         <v>50.0</v>
       </c>
-      <c r="F22" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G22" s="10">
+      <c r="F22" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G22" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="10">
+      <c r="A23" s="17">
         <v>22.0</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="9">
         <v>21.0</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="4">
         <v>4.0</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="21">
         <v>80.0</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="21">
         <v>80.0</v>
       </c>
-      <c r="F23" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G23" s="10">
+      <c r="F23" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G23" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
-      <c r="A24" s="10">
+      <c r="A24" s="17">
         <v>23.0</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="9">
         <v>21.0</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="4">
         <v>5.0</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="21">
         <v>50.0</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="21">
         <v>50.0</v>
       </c>
-      <c r="F24" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G24" s="10">
+      <c r="F24" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G24" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
-      <c r="A25" s="10">
+      <c r="A25" s="17">
         <v>24.0</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="9">
         <v>21.0</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="4">
         <v>6.0</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="21">
         <v>40.0</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="21">
         <v>40.0</v>
       </c>
-      <c r="F25" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G25" s="10">
+      <c r="F25" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G25" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
-      <c r="A26" s="10">
+      <c r="A26" s="17">
         <v>25.0</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="9">
         <v>8.0</v>
       </c>
-      <c r="C26" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D26" s="16">
+      <c r="C26" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D26" s="21">
         <v>70.0</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="21">
         <v>70.0</v>
       </c>
-      <c r="F26" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G26" s="10">
+      <c r="F26" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G26" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
-      <c r="A27" s="10">
+      <c r="A27" s="17">
         <v>26.0</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="9">
         <v>8.0</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="4">
         <v>2.0</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="21">
         <v>60.0</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="21">
         <v>60.0</v>
       </c>
-      <c r="F27" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G27" s="10">
+      <c r="F27" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G27" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="10">
+      <c r="A28" s="17">
         <v>27.0</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="9">
         <v>8.0</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="4">
         <v>3.0</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="21">
         <v>60.0</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="21">
         <v>60.0</v>
       </c>
-      <c r="F28" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G28" s="10">
+      <c r="F28" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G28" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="29" ht="12.75" customHeight="1">
-      <c r="A29" s="10">
+      <c r="A29" s="17">
         <v>28.0</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="9">
         <v>8.0</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="4">
         <v>4.0</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="21">
         <v>80.0</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="21">
         <v>80.0</v>
       </c>
-      <c r="F29" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G29" s="10">
+      <c r="F29" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G29" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="A30" s="10">
+      <c r="A30" s="17">
         <v>29.0</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="9">
         <v>8.0</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="4">
         <v>5.0</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="21">
         <v>60.0</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="21">
         <v>60.0</v>
       </c>
-      <c r="F30" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G30" s="10">
+      <c r="F30" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G30" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="31" ht="12.75" customHeight="1">
-      <c r="A31" s="10">
+      <c r="A31" s="17">
         <v>30.0</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="9">
         <v>8.0</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="4">
         <v>6.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="21">
         <v>50.0</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="21">
         <v>50.0</v>
       </c>
-      <c r="F31" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G31" s="10">
+      <c r="F31" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G31" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="10">
+      <c r="A32" s="17">
         <v>31.0</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="9">
         <v>30.0</v>
       </c>
-      <c r="C32" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D32" s="16">
+      <c r="C32" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D32" s="21">
         <v>40.0</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="21">
         <v>40.0</v>
       </c>
-      <c r="F32" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G32" s="10">
+      <c r="F32" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G32" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="10">
+      <c r="A33" s="17">
         <v>32.0</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="9">
         <v>30.0</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="4">
         <v>2.0</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="21">
         <v>30.0</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="21">
         <v>30.0</v>
       </c>
-      <c r="F33" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G33" s="10">
+      <c r="F33" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G33" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="10">
+      <c r="A34" s="17">
         <v>33.0</v>
       </c>
-      <c r="B34" s="6">
+      <c r="B34" s="9">
         <v>30.0</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="4">
         <v>3.0</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="21">
         <v>50.0</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="21">
         <v>50.0</v>
       </c>
-      <c r="F34" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G34" s="10">
+      <c r="F34" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G34" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="10">
+      <c r="A35" s="17">
         <v>34.0</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35" s="9">
         <v>30.0</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="4">
         <v>4.0</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="21">
         <v>90.0</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="21">
         <v>90.0</v>
       </c>
-      <c r="F35" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G35" s="10">
+      <c r="F35" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G35" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="10">
+      <c r="A36" s="17">
         <v>35.0</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="9">
         <v>30.0</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="4">
         <v>5.0</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="21">
         <v>70.0</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="21">
         <v>70.0</v>
       </c>
-      <c r="F36" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G36" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="K36" s="19"/>
+      <c r="F36" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G36" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="K36" s="29"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="10">
+      <c r="A37" s="17">
         <v>36.0</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B37" s="9">
         <v>30.0</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="4">
         <v>6.0</v>
       </c>
-      <c r="D37" s="16">
+      <c r="D37" s="21">
         <v>50.0</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="21">
         <v>50.0</v>
       </c>
-      <c r="F37" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G37" s="10">
+      <c r="F37" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G37" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="10">
+      <c r="A38" s="17">
         <v>37.0</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="9">
         <v>7.0</v>
       </c>
-      <c r="C38" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D38" s="16">
+      <c r="C38" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D38" s="21">
         <v>30.0</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E38" s="21">
         <v>30.0</v>
       </c>
-      <c r="F38" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G38" s="10">
+      <c r="F38" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G38" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="10">
+      <c r="A39" s="17">
         <v>38.0</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39" s="9">
         <v>7.0</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="4">
         <v>2.0</v>
       </c>
-      <c r="D39" s="16">
+      <c r="D39" s="21">
         <v>20.0</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E39" s="21">
         <v>20.0</v>
       </c>
-      <c r="F39" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G39" s="10">
+      <c r="F39" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G39" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="10">
+      <c r="A40" s="17">
         <v>39.0</v>
       </c>
-      <c r="B40" s="6">
+      <c r="B40" s="9">
         <v>7.0</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="4">
         <v>3.0</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="21">
         <v>30.0</v>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="21">
         <v>30.0</v>
       </c>
-      <c r="F40" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G40" s="10">
+      <c r="F40" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G40" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="10">
+      <c r="A41" s="17">
         <v>40.0</v>
       </c>
-      <c r="B41" s="6">
+      <c r="B41" s="9">
         <v>7.0</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="4">
         <v>4.0</v>
       </c>
-      <c r="D41" s="16">
+      <c r="D41" s="21">
         <v>90.0</v>
       </c>
-      <c r="E41" s="16">
+      <c r="E41" s="21">
         <v>90.0</v>
       </c>
-      <c r="F41" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G41" s="10">
+      <c r="F41" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G41" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="10">
+      <c r="A42" s="17">
         <v>41.0</v>
       </c>
-      <c r="B42" s="6">
+      <c r="B42" s="9">
         <v>7.0</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="4">
         <v>5.0</v>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="21">
         <v>80.0</v>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="21">
         <v>80.0</v>
       </c>
-      <c r="F42" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G42" s="10">
+      <c r="F42" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G42" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="10">
+      <c r="A43" s="17">
         <v>42.0</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43" s="9">
         <v>7.0</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="4">
         <v>6.0</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="21">
         <v>50.0</v>
       </c>
-      <c r="E43" s="16">
+      <c r="E43" s="21">
         <v>50.0</v>
       </c>
-      <c r="F43" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G43" s="10">
+      <c r="F43" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G43" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="10">
+      <c r="A44" s="17">
         <v>43.0</v>
       </c>
-      <c r="B44" s="6">
+      <c r="B44" s="9">
         <v>13.0</v>
       </c>
-      <c r="C44" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D44" s="16">
+      <c r="C44" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D44" s="21">
         <v>50.0</v>
       </c>
-      <c r="E44" s="16">
+      <c r="E44" s="21">
         <v>50.0</v>
       </c>
-      <c r="F44" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G44" s="10">
+      <c r="F44" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G44" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="10">
+      <c r="A45" s="17">
         <v>44.0</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45" s="9">
         <v>13.0</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="4">
         <v>2.0</v>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="21">
         <v>40.0</v>
       </c>
-      <c r="E45" s="16">
+      <c r="E45" s="21">
         <v>40.0</v>
       </c>
-      <c r="F45" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G45" s="10">
+      <c r="F45" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G45" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="10">
+      <c r="A46" s="17">
         <v>45.0</v>
       </c>
-      <c r="B46" s="6">
+      <c r="B46" s="9">
         <v>13.0</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="4">
         <v>3.0</v>
       </c>
-      <c r="D46" s="16">
+      <c r="D46" s="21">
         <v>70.0</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E46" s="21">
         <v>70.0</v>
       </c>
-      <c r="F46" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G46" s="10">
+      <c r="F46" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G46" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="10">
+      <c r="A47" s="17">
         <v>46.0</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="9">
         <v>13.0</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="4">
         <v>4.0</v>
       </c>
-      <c r="D47" s="16">
+      <c r="D47" s="21">
         <v>80.0</v>
       </c>
-      <c r="E47" s="16">
+      <c r="E47" s="21">
         <v>80.0</v>
       </c>
-      <c r="F47" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G47" s="10">
+      <c r="F47" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G47" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="10">
+      <c r="A48" s="17">
         <v>47.0</v>
       </c>
-      <c r="B48" s="6">
+      <c r="B48" s="9">
         <v>13.0</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="4">
         <v>5.0</v>
       </c>
-      <c r="D48" s="16">
+      <c r="D48" s="21">
         <v>70.0</v>
       </c>
-      <c r="E48" s="16">
+      <c r="E48" s="21">
         <v>70.0</v>
       </c>
-      <c r="F48" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G48" s="10">
+      <c r="F48" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G48" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="10">
+      <c r="A49" s="17">
         <v>48.0</v>
       </c>
-      <c r="B49" s="6">
+      <c r="B49" s="9">
         <v>13.0</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="4">
         <v>6.0</v>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="21">
         <v>60.0</v>
       </c>
-      <c r="E49" s="16">
+      <c r="E49" s="21">
         <v>60.0</v>
       </c>
-      <c r="F49" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G49" s="10">
+      <c r="F49" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G49" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="A50" s="10">
+      <c r="A50" s="17">
         <v>49.0</v>
       </c>
-      <c r="B50" s="6">
+      <c r="B50" s="9">
         <v>25.0</v>
       </c>
-      <c r="C50" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D50" s="16">
+      <c r="C50" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D50" s="21">
         <v>60.0</v>
       </c>
-      <c r="E50" s="16">
+      <c r="E50" s="21">
         <v>60.0</v>
       </c>
-      <c r="F50" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G50" s="10">
+      <c r="F50" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G50" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="A51" s="10">
+      <c r="A51" s="17">
         <v>50.0</v>
       </c>
-      <c r="B51" s="6">
+      <c r="B51" s="9">
         <v>25.0</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="4">
         <v>2.0</v>
       </c>
-      <c r="D51" s="16">
+      <c r="D51" s="21">
         <v>50.0</v>
       </c>
-      <c r="E51" s="16">
+      <c r="E51" s="21">
         <v>50.0</v>
       </c>
-      <c r="F51" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G51" s="10">
+      <c r="F51" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G51" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="A52" s="10">
+      <c r="A52" s="17">
         <v>51.0</v>
       </c>
-      <c r="B52" s="6">
+      <c r="B52" s="9">
         <v>25.0</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="4">
         <v>3.0</v>
       </c>
-      <c r="D52" s="16">
+      <c r="D52" s="21">
         <v>80.0</v>
       </c>
-      <c r="E52" s="16">
+      <c r="E52" s="21">
         <v>80.0</v>
       </c>
-      <c r="F52" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G52" s="10">
+      <c r="F52" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G52" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="A53" s="10">
+      <c r="A53" s="17">
         <v>52.0</v>
       </c>
-      <c r="B53" s="6">
+      <c r="B53" s="9">
         <v>25.0</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="4">
         <v>4.0</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="21">
         <v>80.0</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="21">
         <v>80.0</v>
       </c>
-      <c r="F53" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G53" s="10">
+      <c r="F53" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G53" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="A54" s="10">
+      <c r="A54" s="17">
         <v>53.0</v>
       </c>
-      <c r="B54" s="6">
+      <c r="B54" s="9">
         <v>25.0</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="4">
         <v>5.0</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D54" s="21">
         <v>70.0</v>
       </c>
-      <c r="E54" s="16">
+      <c r="E54" s="21">
         <v>70.0</v>
       </c>
-      <c r="F54" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G54" s="10">
+      <c r="F54" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G54" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="A55" s="10">
+      <c r="A55" s="17">
         <v>54.0</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="9">
         <v>25.0</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="4">
         <v>6.0</v>
       </c>
-      <c r="D55" s="16">
+      <c r="D55" s="21">
         <v>70.0</v>
       </c>
-      <c r="E55" s="16">
+      <c r="E55" s="21">
         <v>70.0</v>
       </c>
-      <c r="F55" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G55" s="10">
+      <c r="F55" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G55" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="A56" s="10">
+      <c r="A56" s="17">
         <v>55.0</v>
       </c>
-      <c r="B56" s="6">
+      <c r="B56" s="9">
         <v>27.0</v>
       </c>
-      <c r="C56" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D56" s="16">
+      <c r="C56" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D56" s="21">
         <v>50.0</v>
       </c>
-      <c r="E56" s="16">
+      <c r="E56" s="21">
         <v>50.0</v>
       </c>
-      <c r="F56" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G56" s="10">
+      <c r="F56" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G56" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="A57" s="10">
+      <c r="A57" s="17">
         <v>56.0</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B57" s="9">
         <v>27.0</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="4">
         <v>2.0</v>
       </c>
-      <c r="D57" s="16">
+      <c r="D57" s="21">
         <v>40.0</v>
       </c>
-      <c r="E57" s="16">
+      <c r="E57" s="21">
         <v>40.0</v>
       </c>
-      <c r="F57" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G57" s="10">
+      <c r="F57" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G57" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="A58" s="10">
+      <c r="A58" s="17">
         <v>57.0</v>
       </c>
-      <c r="B58" s="6">
+      <c r="B58" s="9">
         <v>27.0</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="4">
         <v>3.0</v>
       </c>
-      <c r="D58" s="16">
+      <c r="D58" s="21">
         <v>50.0</v>
       </c>
-      <c r="E58" s="16">
+      <c r="E58" s="21">
         <v>50.0</v>
       </c>
-      <c r="F58" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G58" s="10">
+      <c r="F58" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G58" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="A59" s="10">
+      <c r="A59" s="17">
         <v>58.0</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B59" s="9">
         <v>27.0</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59" s="4">
         <v>4.0</v>
       </c>
-      <c r="D59" s="16">
+      <c r="D59" s="21">
         <v>70.0</v>
       </c>
-      <c r="E59" s="16">
+      <c r="E59" s="21">
         <v>70.0</v>
       </c>
-      <c r="F59" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G59" s="10">
+      <c r="F59" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G59" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="A60" s="10">
+      <c r="A60" s="17">
         <v>59.0</v>
       </c>
-      <c r="B60" s="6">
+      <c r="B60" s="9">
         <v>27.0</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60" s="4">
         <v>5.0</v>
       </c>
-      <c r="D60" s="16">
+      <c r="D60" s="21">
         <v>60.0</v>
       </c>
-      <c r="E60" s="16">
+      <c r="E60" s="21">
         <v>60.0</v>
       </c>
-      <c r="F60" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G60" s="10">
+      <c r="F60" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G60" s="17">
         <v>1.0</v>
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="10">
+      <c r="A61" s="17">
         <v>60.0</v>
       </c>
-      <c r="B61" s="6">
+      <c r="B61" s="9">
         <v>27.0</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="4">
         <v>6.0</v>
       </c>
-      <c r="D61" s="16">
+      <c r="D61" s="21">
         <v>50.0</v>
       </c>
-      <c r="E61" s="16">
+      <c r="E61" s="21">
         <v>50.0</v>
       </c>
-      <c r="F61" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="G61" s="10">
+      <c r="F61" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="G61" s="17">
         <v>1.0</v>
       </c>
     </row>
